--- a/data/trans_dic/IP31KM07_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM07_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>81,94; 96,27</t>
+          <t>73,8; 90,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74,59; 90,6</t>
+          <t>82,48; 96,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,95; 92,1</t>
+          <t>82,28; 92,48</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,81%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,67; 94,2</t>
+          <t>83,63; 92,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83,74; 92,79</t>
+          <t>85,55; 93,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,72; 92,56</t>
+          <t>86,48; 92,38</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,54%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,3; 92,75</t>
+          <t>84,72; 93,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,84; 93,43</t>
+          <t>85,3; 93,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,21; 92,02</t>
+          <t>86,24; 92,28</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>58,41; 92,3</t>
+          <t>80,7; 90,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>77,47; 90,08</t>
+          <t>85,57; 93,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,19; 89,21</t>
+          <t>84,41; 91,17</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>89,06%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>73,71; 91,28</t>
+          <t>84,85; 90,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83,68; 89,68</t>
+          <t>88,14; 92,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,77; 89,15</t>
+          <t>87,15; 90,82</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>76</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>31161</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>39120</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80379</t>
+          <t>70281</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>38098; 44763</t>
+          <t>27628; 33965</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33780; 41027</t>
+          <t>35204; 41073</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>75217; 84527</t>
+          <t>65920; 74090</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>234</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>144904</t>
+          <t>139802</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>161682</t>
+          <t>131915</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>306586</t>
+          <t>271718</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>138069; 150055</t>
+          <t>131336; 145364</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>152374; 168838</t>
+          <t>124493; 136442</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>295930; 315872</t>
+          <t>261655; 279503</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>210</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>153045</t>
+          <t>178736</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>190628</t>
+          <t>156857</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>343675</t>
+          <t>335592</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>140716; 160525</t>
+          <t>169557; 186114</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>180272; 198520</t>
+          <t>149000; 163565</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>328536; 354802</t>
+          <t>323211; 345879</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>310</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>226416</t>
+          <t>253652</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>257745</t>
+          <t>231053</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>484161</t>
+          <t>484705</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>160190; 253149</t>
+          <t>235824; 265568</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>236285; 274749</t>
+          <t>218490; 238819</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>400781; 516764</t>
+          <t>462180; 499206</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>830</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>566831</t>
+          <t>603352</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>647971</t>
+          <t>558945</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1214801</t>
+          <t>1162296</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>481405; 596171</t>
+          <t>582763; 619772</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>623159; 667911</t>
+          <t>544874; 570790</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1129051; 1246222</t>
+          <t>1137367; 1185217</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM07_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM07_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman legumbres más de una vez a la semana (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>83,24%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>91,66%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>73,8; 90,73</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>82,48; 96,23</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>82,28; 92,48</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>89,02%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>90,65%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>89,81%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>83,63; 92,56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>85,55; 93,76</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>86,48; 92,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>89,31%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>89,54%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>84,72; 93,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>85,3; 93,64</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>86,24; 92,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>86,8%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>90,49%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>88,52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>80,7; 90,88</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>85,57; 93,53</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>84,41; 91,17</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>87,85%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>90,41%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>89,06%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>84,85; 90,24</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>88,14; 92,33</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>87,15; 90,82</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.8324126705416004</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.916559134015306</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.8772406573243023</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>31161</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>39120</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>70281</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.738035098712142</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.8248187229401659</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.8228038537519639</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>27628; 33965</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>35204; 41073</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>65920; 74090</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.9072961076870238</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9623252514707503</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9247866216782694</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.8902231620351923</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9065224992496335</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.8980624130436109</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>139802</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>131915</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>271718</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.8363103665929577</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.855515678414787</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.8648038184921338</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>131336; 145364</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>124493; 136442</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>261655; 279503</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9256379509207627</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9376297350487033</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9237945538555603</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.8931151414613397</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.8980070394368834</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.8953949794524558</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>178736</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>156857</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>335592</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.847249673316817</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.8530300951764755</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.8623609607515277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>169557; 186114</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>149000; 163565</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>323211; 345879</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.9299865930808857</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9364094505536451</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.9228411075149832</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.8680153363863047</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.9048945639993622</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8852128518802753</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>253652</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>231053</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>484705</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.8070064111347851</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.8556933626322739</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.8440755727446712</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>235824; 265568</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>218490; 238819</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>462180; 499206</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.9087910835931519</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9353107976063016</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.911694689422608</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1672</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.8784661877081333</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9041370287362955</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.890626746867701</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>603352</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>558945</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1162296</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.8484900358767513</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.8813762514338412</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.8715245833372017</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>582763; 619772</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>544874; 570790</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1137367; 1185217</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9023731598603605</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.9232969367772014</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9081909304307036</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman legumbres más de una vez a la semana (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>31161</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>39120</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>70281</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>27628</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>35204</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>65920</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>33965</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>41073</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>74090</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>248</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>234</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>139802</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>131915</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>271718</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>131336</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>124493</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>261655</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>145364</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>136442</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>279503</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>221</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>178736</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>156857</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>335592</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>169557</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>149000</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>323211</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>186114</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>163565</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>345879</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>307</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>253652</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>231053</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>484705</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>235824</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>218490</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>462180</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>265568</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>238819</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>499206</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>842</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>830</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>603352</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>558945</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1162296</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>582763</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>544874</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1137367</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>619772</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>570790</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1185217</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>